--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104498_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104498_W5.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.896</v>
+        <v>6.463</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6332</v>
+        <v>5.9494</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2629</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>6.866</v>
+        <v>6.8613</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1774</v>
+        <v>2.1798</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6886</v>
+        <v>4.6815</v>
       </c>
       <c r="J2" t="n">
-        <v>7.6435</v>
+        <v>7.6173</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9741</v>
+        <v>1.965</v>
       </c>
       <c r="L2" t="n">
-        <v>5.6694</v>
+        <v>5.6523</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7776</v>
+        <v>-0.756</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9699</v>
+        <v>-0.3984</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1352</v>
+        <v>0.0827</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1031</v>
+        <v>3.0163</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9016</v>
+        <v>2.7028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2015</v>
+        <v>0.3135</v>
       </c>
       <c r="G3" t="n">
-        <v>2.524</v>
+        <v>2.5148</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.44</v>
+        <v>-0.4449</v>
       </c>
       <c r="I3" t="n">
-        <v>2.964</v>
+        <v>2.9597</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1684</v>
+        <v>3.1433</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3558</v>
+        <v>3.3436</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6444</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0989</v>
+        <v>0.0267</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1603</v>
+        <v>-0.0049</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. RUSSELL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6659</v>
+        <v>2.7757</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0855</v>
+        <v>0.3567</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5804</v>
+        <v>2.4189</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3824</v>
+        <v>2.1501</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6406</v>
+        <v>1.5606</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2582</v>
+        <v>0.5894</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5709</v>
+        <v>1.9613</v>
       </c>
       <c r="K4" t="n">
-        <v>1.4373</v>
+        <v>1.2024</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.759</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1885</v>
+        <v>0.1887</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2033</v>
+        <v>0.3583</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3918</v>
+        <v>-0.1695</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>3.1868</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4027</v>
+        <v>0.281</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8075</v>
+        <v>0.1482</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5952</v>
+        <v>0.1328</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7071</v>
+        <v>-1.4764</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7071</v>
+        <v>-0.387</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.4141</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1482</v>
+        <v>1.7886</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3626</v>
+        <v>1.4253</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7856</v>
+        <v>0.3633</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4029</v>
+        <v>0.382</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6047</v>
+        <v>1.6454</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0076</v>
+        <v>-1.2634</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1389</v>
+        <v>0.5512</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4644</v>
+        <v>1.4307</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6744</v>
+        <v>-0.8794999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0.736</v>
+        <v>-0.1692</v>
       </c>
       <c r="N5" t="n">
-        <v>1.0691</v>
+        <v>0.2148</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3331</v>
+        <v>-0.384</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1294</v>
+        <v>0.5157</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4748</v>
+        <v>0.1716</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6042999999999999</v>
+        <v>0.3441</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0927</v>
+        <v>-0.7025</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. RUSSELL</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9708</v>
+        <v>1.7299</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6034</v>
+        <v>-0.0116</v>
       </c>
       <c r="F6" t="n">
-        <v>2.5741</v>
+        <v>1.7415</v>
       </c>
       <c r="G6" t="n">
-        <v>2.18</v>
+        <v>-0.4049</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5804</v>
+        <v>0.6005</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5997</v>
+        <v>-1.0054</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0112</v>
+        <v>-1.1541</v>
       </c>
       <c r="K6" t="n">
-        <v>1.2357</v>
+        <v>-0.4761</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7755</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1688</v>
+        <v>0.7492</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3446</v>
+        <v>1.0766</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1759</v>
+        <v>-0.3275</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>1.5934</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1757</v>
+        <v>1.8211</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5456</v>
+        <v>-0.5481</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.868</v>
+        <v>0.1228</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3224</v>
+        <v>-0.671</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4783</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3856</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAKHO</t>
+          <t>K. COOK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6197</v>
+        <v>1.5924</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2372</v>
+        <v>0.1517</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3826</v>
+        <v>1.4407</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6287</v>
+        <v>-0.8328</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.205</v>
+        <v>1.7633</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4238</v>
+        <v>-2.5961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1302</v>
+        <v>-0.2463</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.09370000000000001</v>
+        <v>1.7064</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2239</v>
+        <v>-1.9528</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.759</v>
+        <v>-0.5865</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1113</v>
+        <v>0.0568</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6805</v>
+        <v>2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7533</v>
+        <v>0.1473</v>
       </c>
       <c r="T7" t="n">
-        <v>2.2411</v>
+        <v>-0.1467</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5122</v>
+        <v>0.294</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1853</v>
+        <v>0.2292</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="8">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2168</v>
+        <v>1.5493</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5663</v>
+        <v>-0.2899</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7831</v>
+        <v>1.8391</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4094</v>
+        <v>3.4157</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9811</v>
+        <v>0.9876</v>
       </c>
       <c r="I8" t="n">
-        <v>2.4283</v>
+        <v>2.4281</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2834</v>
+        <v>3.269</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9351</v>
+        <v>0.9308</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3482</v>
+        <v>2.3383</v>
       </c>
       <c r="M8" t="n">
-        <v>0.126</v>
+        <v>0.1467</v>
       </c>
       <c r="N8" t="n">
-        <v>0.046</v>
+        <v>0.0568</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9923</v>
+        <v>-0.6584</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6079</v>
+        <v>-0.3022</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3844</v>
+        <v>-0.3562</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. QUINTELA</t>
+          <t>M. ANDRIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9267</v>
+        <v>1.3925</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.2931</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1188</v>
+        <v>1.0995</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0586</v>
+        <v>-0.1033</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3145</v>
+        <v>-1.1921</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3732</v>
+        <v>1.0888</v>
       </c>
       <c r="J9" t="n">
+        <v>0.2238</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-1.4069</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.6308</v>
+      </c>
+      <c r="M9" t="n">
+        <v>-0.3271</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.5419</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.7316</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-0.2276</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.9592</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.2854</v>
+      </c>
+      <c r="V9" t="n">
+        <v>-1.2472</v>
+      </c>
+      <c r="W9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>-0.0586</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.3145</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-0.3732</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.2268</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-0.2268</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4537</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.7585</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.8741</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.1155</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0.1607</v>
-      </c>
       <c r="X9" t="n">
-        <v>-0.1607</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ANDRIC</t>
+          <t>E. QUINTELA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8798</v>
+        <v>0.6403</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0008</v>
+        <v>0.4527</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8791</v>
+        <v>0.1876</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1061</v>
+        <v>-0.0565</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1963</v>
+        <v>0.3159</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0902</v>
+        <v>-0.3724</v>
       </c>
       <c r="J10" t="n">
-        <v>0.2397</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3995</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6392</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3458</v>
+        <v>-0.0565</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2033</v>
+        <v>0.3159</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.549</v>
+        <v>-0.3724</v>
       </c>
       <c r="P10" t="n">
-        <v>2.722</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9488</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4827</v>
+        <v>0.4692</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0121</v>
+        <v>0.5225</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4706</v>
+        <v>-0.0534</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. COOK</t>
+          <t>J. SAKHO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5512</v>
+        <v>-0.3288</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7048</v>
+        <v>-0.1141</v>
       </c>
       <c r="F11" t="n">
-        <v>1.256</v>
+        <v>-0.2147</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.8094</v>
+        <v>-0.6211</v>
       </c>
       <c r="H11" t="n">
-        <v>1.7604</v>
+        <v>-0.2012</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5698</v>
+        <v>-0.4199</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2077</v>
+        <v>0.1233</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7144</v>
+        <v>-0.1002</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9221</v>
+        <v>0.2234</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6017</v>
+        <v>-0.7444</v>
       </c>
       <c r="N11" t="n">
-        <v>0.046</v>
+        <v>-0.1011</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
-        <v>2.0415</v>
+        <v>0.6829</v>
       </c>
       <c r="Q11" t="n">
+        <v>-1.1382</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.8211</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.7884</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9008</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.8875999999999999</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-2.1789</v>
+      </c>
+      <c r="W11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.0415</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-0.9058</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1.0434</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.1376</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0.2249</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0.5463</v>
-      </c>
       <c r="X11" t="n">
-        <v>-0.3214</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4457</v>
+        <v>-0.697</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4645</v>
+        <v>0.0374</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9103</v>
+        <v>-0.7343</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3274</v>
+        <v>0.3219</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4962</v>
+        <v>-0.505</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8237</v>
+        <v>0.8269</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8387</v>
+        <v>0.823</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0551</v>
+        <v>0.041</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5113</v>
+        <v>-0.5011</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O12" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3856</v>
+        <v>0.1405</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4386</v>
+        <v>0.037</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0529</v>
+        <v>0.1035</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.3604</v>
+        <v>-1.0635</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6601</v>
+        <v>-3.6072</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2996</v>
+        <v>2.5437</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.4501</v>
+        <v>-3.464</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.899</v>
+        <v>-0.8935</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5511</v>
+        <v>-2.5704</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.6348</v>
+        <v>-3.6671</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4169</v>
+        <v>-1.4242</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.2179</v>
+        <v>-2.243</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1847</v>
+        <v>0.2032</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P13" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R13" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4055</v>
+        <v>-0.1035</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7984</v>
+        <v>0.2876</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.607</v>
+        <v>-0.391</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.1721</v>
+        <v>18.8587</v>
       </c>
       <c r="E14" t="n">
-        <v>6.9588</v>
+        <v>7.346299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11.2134</v>
+        <v>11.5124</v>
       </c>
       <c r="G14" t="n">
-        <v>10.2334</v>
+        <v>10.1632</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8226</v>
+        <v>5.816400000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>4.410799999999998</v>
+        <v>4.3468</v>
       </c>
       <c r="J14" t="n">
-        <v>12.9046</v>
+        <v>12.6447</v>
       </c>
       <c r="K14" t="n">
-        <v>3.789800000000001</v>
+        <v>3.668600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>9.1149</v>
+        <v>8.9762</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6714</v>
+        <v>-2.4815</v>
       </c>
       <c r="N14" t="n">
-        <v>2.0327</v>
+        <v>2.147699999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.7041</v>
+        <v>-4.629499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>11.3417</v>
+        <v>11.3816</v>
       </c>
       <c r="Q14" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6833</v>
+        <v>22.7632</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9678</v>
+        <v>1.6719</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8319000000000001</v>
+        <v>1.5524</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1361000000000001</v>
+        <v>0.1193</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.3707</v>
+        <v>-4.3577</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5638</v>
+        <v>4.5305</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.9344</v>
+        <v>-8.888399999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2365</v>
+        <v>2.6474</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7989</v>
+        <v>2.2344</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4375</v>
+        <v>0.413</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6705</v>
+        <v>1.6794</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2353</v>
+        <v>-0.2273</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9059</v>
+        <v>1.9067</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6289</v>
+        <v>2.6062</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0968</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5321</v>
+        <v>2.5168</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9584</v>
+        <v>-0.9268</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3321</v>
+        <v>-0.3168</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6263</v>
+        <v>-0.61</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7782</v>
+        <v>-0.3703</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.747</v>
+        <v>-0.2744</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0312</v>
+        <v>-0.0959</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1797</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0663</v>
+        <v>1.115</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1134</v>
+        <v>-0.188</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0261</v>
+        <v>0.9109</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0562</v>
+        <v>0.2008</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0823</v>
+        <v>0.7101</v>
       </c>
       <c r="J16" t="n">
-        <v>1.214</v>
+        <v>1.1803</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1345</v>
+        <v>0.0862</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0795</v>
+        <v>1.0941</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1879</v>
+        <v>-0.2694</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1908</v>
+        <v>0.1146</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0028</v>
+        <v>-0.384</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3408</v>
+        <v>0.195</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8257</v>
+        <v>-0.0653</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4848</v>
+        <v>0.2603</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8678</v>
+        <v>-1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0285</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0445</v>
+        <v>0.8578</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6596</v>
+        <v>0.4438</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6151</v>
+        <v>0.4139</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9157999999999999</v>
+        <v>1.0338</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1962</v>
+        <v>-0.0601</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7196</v>
+        <v>1.0939</v>
       </c>
       <c r="J17" t="n">
-        <v>1.198</v>
+        <v>1.1854</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0866</v>
+        <v>0.1132</v>
       </c>
       <c r="L17" t="n">
-        <v>1.1114</v>
+        <v>1.0722</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2822</v>
+        <v>-0.1516</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1096</v>
+        <v>-0.1733</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3918</v>
+        <v>0.0217</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6859</v>
+        <v>0.0013</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5383</v>
+        <v>0.2388</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1476</v>
+        <v>-0.2375</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-0.8603</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0927</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z. HANKINS</t>
+          <t>I. AURRECOECHEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0363</v>
+        <v>-0.2111</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9425</v>
+        <v>-0.9144</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9788</v>
+        <v>0.7033</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1833</v>
+        <v>0.3187</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6262</v>
+        <v>0.0028</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3159</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.8693</v>
+        <v>0.0172</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0186</v>
+        <v>0.0172</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1493</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.314</v>
+        <v>0.3014</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3923</v>
+        <v>-0.0144</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7063</v>
+        <v>0.3159</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9662</v>
+        <v>0.223</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0344</v>
+        <v>0.0487</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9318</v>
+        <v>0.1743</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA</t>
+          <t>Z. HANKINS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3889</v>
+        <v>-0.7742</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0257</v>
+        <v>-2.4309</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6368</v>
+        <v>1.6567</v>
       </c>
       <c r="G19" t="n">
-        <v>0.316</v>
+        <v>-1.177</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0014</v>
+        <v>-0.6261</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3145</v>
+        <v>-0.5508999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0173</v>
+        <v>-0.8788</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0173</v>
+        <v>-1.0277</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1489</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2986</v>
+        <v>-0.2982</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0159</v>
+        <v>0.4016</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3145</v>
+        <v>-0.6998</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R19" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0417</v>
+        <v>1.1556</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0696</v>
+        <v>0.5664</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1113</v>
+        <v>0.5891999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2144</v>
+        <v>-1.0721</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3597</v>
+        <v>0.9409</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5741</v>
+        <v>-2.013</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5669</v>
+        <v>0.5817</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0275</v>
+        <v>-0.0205</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5945</v>
+        <v>0.6021</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1895</v>
+        <v>2.1838</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3983</v>
+        <v>0.3964</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7912</v>
+        <v>1.7874</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6225</v>
+        <v>-1.6022</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4258</v>
+        <v>-0.4169</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0743</v>
+        <v>0.0487</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6956</v>
+        <v>-0.1048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3787</v>
+        <v>0.1535</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4613</v>
+        <v>-2.1983</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1152</v>
+        <v>-2.5185</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.346</v>
+        <v>0.3202</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.7542</v>
+        <v>-3.7443</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9017</v>
+        <v>-1.9068</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8524</v>
+        <v>-1.8375</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.8199</v>
+        <v>-2.848</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.3964</v>
+        <v>-1.4176</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9343</v>
+        <v>-0.8963</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5053</v>
+        <v>-0.4891</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.429</v>
+        <v>-0.4072</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1043</v>
+        <v>0.1685</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6684</v>
+        <v>0.3178</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7728</v>
+        <v>-0.1493</v>
       </c>
       <c r="V21" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="W21" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1389</v>
+        <v>-2.6257</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7161</v>
+        <v>-1.3995</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4228</v>
+        <v>-1.2261</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4654</v>
+        <v>0.4865</v>
       </c>
       <c r="H22" t="n">
-        <v>1.6088</v>
+        <v>1.6166</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1434</v>
+        <v>-1.13</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4019</v>
+        <v>2.3869</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4451</v>
+        <v>0.4392</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.9365</v>
+        <v>-1.9004</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.348</v>
+        <v>-0.3312</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.5885</v>
+        <v>-1.5692</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0676</v>
+        <v>-0.5596</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2329</v>
+        <v>-0.0785</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4694</v>
+        <v>-4.0683</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3553</v>
+        <v>-2.2638</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1141</v>
+        <v>-1.8045</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.6077</v>
+        <v>-2.5911</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.443</v>
+        <v>-1.4418</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1647</v>
+        <v>-1.1493</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5057</v>
+        <v>-0.5168</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6549</v>
+        <v>-0.6657</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.102</v>
+        <v>-2.0744</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.314</v>
+        <v>-1.2982</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.019</v>
+        <v>-0.5863</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8538</v>
+        <v>0.1317</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6789</v>
+        <v>-4.7018</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.0792</v>
+        <v>-3.3433</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5997</v>
+        <v>-1.3585</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5552</v>
+        <v>-2.555</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2495</v>
+        <v>-0.2553</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3056</v>
+        <v>-2.2997</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2876</v>
+        <v>-0.3067</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3494</v>
+        <v>0.334</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6371</v>
+        <v>-0.6407</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.2675</v>
+        <v>-2.2483</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S24" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0071</v>
       </c>
       <c r="T24" t="n">
-        <v>0.248</v>
+        <v>0.0136</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2395</v>
+        <v>-0.0207</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.3172</v>
+        <v>-5.363</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8639</v>
+        <v>-3.3761</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4533</v>
+        <v>-1.9869</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.0937</v>
+        <v>-5.1066</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.0892</v>
+        <v>-3.0985</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0045</v>
+        <v>-2.0082</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.4958</v>
+        <v>-2.528</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.0025</v>
+        <v>-2.0209</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.598</v>
+        <v>-2.5786</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.5113</v>
+        <v>-1.5011</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3663</v>
+        <v>0.3355</v>
       </c>
       <c r="T25" t="n">
-        <v>0.8075</v>
+        <v>0.3388</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4413</v>
+        <v>-0.0033</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-18.172</v>
+        <v>-16.5824</v>
       </c>
       <c r="E26" t="n">
-        <v>-11.2134</v>
+        <v>-11.5124</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.958600000000001</v>
+        <v>-5.0699</v>
       </c>
       <c r="G26" t="n">
-        <v>-10.2334</v>
+        <v>-10.163</v>
       </c>
       <c r="H26" t="n">
-        <v>-5.8222</v>
+        <v>-5.8162</v>
       </c>
       <c r="I26" t="n">
-        <v>-4.410800000000001</v>
+        <v>-4.3469</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6713</v>
+        <v>2.4815</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.0327</v>
+        <v>-2.1477</v>
       </c>
       <c r="L26" t="n">
-        <v>4.704199999999999</v>
+        <v>4.6294</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.9047</v>
+        <v>-12.6448</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.7897</v>
+        <v>-3.6684</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.1151</v>
+        <v>-8.976099999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-11.3416</v>
+        <v>-11.3816</v>
       </c>
       <c r="Q26" t="n">
-        <v>-22.6833</v>
+        <v>-22.7632</v>
       </c>
       <c r="R26" t="n">
-        <v>11.3415</v>
+        <v>11.3815</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9678000000000004</v>
+        <v>0.6042999999999998</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1359</v>
+        <v>-0.1194999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8318999999999999</v>
+        <v>0.7237999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>4.3706</v>
+        <v>4.358</v>
       </c>
       <c r="W26" t="n">
-        <v>8.9344</v>
+        <v>8.888499999999999</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.5637</v>
+        <v>-4.5305</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104498_W5.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104498_W5.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-8.888399999999999</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104498_W5.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.5305</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
